--- a/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
+++ b/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>64/100</t>
+          <t>66/100</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime · fiche_non_identifiee · surface_a_ventiler · occupation_a_confirmer</t>
+          <t>loyer_estime · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="29" t="inlineStr">
         <is>
-          <t>RUE AUGUSTE BLANCHE - LOCAL POLYVALENT IDÉAL STUDIO / STOCKAGE Situé rue Auguste Blanche, ce local commercial de 145,50 m² offre de nombreuses possibilités d'aménagement. Il convient parfaitement pour un studio d'enregistrement, un studio photo, ou encore un espace de stockage. Le bien se compose d'un vaste open space de 108 m², d'un bureau indépendant, d'une réserve technique, d'un vestiaire, de sanitaires. Une cave en sous-sol complète ce bien. Informations financières : Prix net vendeur : 360 000 euros. Honoraires d'agence (à la charge de l'acquéreur) : 15 000 euros TTC (3,95 %). Prix de vente HAI : 375 000 euros Charges annuelles : 3 200 euros. Copropriété : 10 lots. Un bien rare offrant de beaux volumes et une grande modularité, idéal pour les professionnels à la recherche d'un espace fonctionnel. Contact : REZ-DE-CHAUSSEE.COM au 06 79 80 52 89. Responsabilité éditoriale: Michel VALENTINO (EI), agent commercial de REZ-DE-CHAUSSEE.COM immatriculé au RSAC de PARIS sous le numéro 851 452 516. Copropriété de 10 lots - dont 6 lots habitation. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : www. georisques. gouv. fr</t>
+          <t>RUE AUGUSTE BLANCHE - LOCAL POLYVALENT IDÉAL STUDIO / STOCKAGE Situé rue Auguste Blanche, ce local commercial de 145,50 m² offre de nombreuses possibilités d'aménagement. Il convient parfaitement pour un studio d'enregistrement, un studio photo, ou encore un espace de stockage. Le bien se compose d'un vaste open space de 108 m², d'un bureau indépendant, d'une réserve technique, d'un vestiaire, de sanitaires. Une cave en sous-sol complète ce bien. Informations financières : Prix net vendeur : 360 000 euros. Honoraires d'agence (à la charge de l'acquéreur) : 14 400 euros TTC (4,00 %). Prix de vente HAI : 374 400 euros Charges annuelles : 3 200 euros. Copropriété : 10 lots. Un bien rare offrant de beaux volumes et une grande modularité, idéal pour les professionnels à la recherche d'un espace fonctionnel. Contact : REZ-DE-CHAUSSEE.COM au 06 79 80 52 89. Responsabilité éditoriale: Michel VALENTINO (EI), agent commercial de REZ-DE-CHAUSSEE.COM immatriculé au RSAC de PARIS sous le numéro 851 452 516. Copropriété de 10 lots - dont 6 lots habitation. Les informations sur les risques auxquels ce bien est exposé sont disponibles sur le site Géorisques : www. georisques. gouv. fr</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
+++ b/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>66/100</t>
+          <t>68/100</t>
         </is>
       </c>
       <c r="C58" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
+++ b/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
+++ b/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
+++ b/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
+++ b/docs/dossiers/dossier-puteaux-12e6afd5.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
